--- a/c7/downloads/C7/SkyG-Speed-120-BOM.xlsx
+++ b/c7/downloads/C7/SkyG-Speed-120-BOM.xlsx
@@ -2606,7 +2606,7 @@
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Nylon screw M3 x 12</t>
+          <t>Nylon screw M3 x 8</t>
         </is>
       </c>
       <c r="D50" s="7" t="n">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>Nylon PA66 socket or pan head</t>
+          <t>Nylon PA66 pan head</t>
         </is>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>M3x12 nylon screw</t>
+          <t>M3x8 nylon screw</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="J50" s="8" t="inlineStr">
         <is>
-          <t>A 16 mm screw here reaches the aileron servo</t>
+          <t>A 12 mm screw here reaches the aileron servo arm (found with the screws modelled in the assembly)</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>1.48</v>
@@ -3800,10 +3800,10 @@
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>14.6</v>
+        <v>14.8</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>2</v>
@@ -4112,7 +4112,7 @@
         </is>
       </c>
       <c r="C28" s="7" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>0.12</v>
@@ -4129,7 +4129,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>One aircraft (one aircraft with the N0M nose; N0P is an alternative part): 78.9 g, 12.4 h of printing.</t>
+          <t>One aircraft (one aircraft with the N0M nose; N0P is an alternative part): 79.4 g, 12.5 h of printing.</t>
         </is>
       </c>
     </row>

--- a/c7/downloads/C7/SkyG-Speed-120-BOM.xlsx
+++ b/c7/downloads/C7/SkyG-Speed-120-BOM.xlsx
@@ -1438,7 +1438,7 @@
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Nylon screw M3 x 16</t>
+          <t>Nylon countersunk screw M3 x 16</t>
         </is>
       </c>
       <c r="D24" s="7" t="n">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>Nylon PA66 socket or pan head</t>
+          <t>Nylon PA66 countersunk (flat head, DIN 965 / ISO 7046)</t>
         </is>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>M3x16 nylon screws</t>
+          <t>M3x16 nylon countersunk screw</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>M2 x 6 screws</t>
+          <t>M2 x 6 countersunk screws (joints)</t>
         </is>
       </c>
       <c r="D26" s="7" t="n">
@@ -1537,17 +1537,17 @@
       </c>
       <c r="F26" s="8" t="inlineStr">
         <is>
-          <t>Steel socket/pan head</t>
+          <t>M2 x 6 countersunk (DIN 965), steel</t>
         </is>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>M2x6 screws</t>
+          <t>M2x6 countersunk screws</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>Fuselage joints (3 x 2), into internal bosses (4.5 mm thread)</t>
+          <t>Fuselage joints (3 x 2), flush in countersinks in the skin, into internal bosses (4.5 mm thread)</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Nylon screw M3 x 8</t>
+          <t>Nylon countersunk screw M3 x 8</t>
         </is>
       </c>
       <c r="D50" s="7" t="n">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>Nylon PA66 pan head</t>
+          <t>Nylon PA66 countersunk (flat head, DIN 965 / ISO 7046)</t>
         </is>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>M3x8 nylon screw</t>
+          <t>M3x8 nylon countersunk screw</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
@@ -3800,10 +3800,10 @@
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>14.8</v>
+        <v>14.6</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>2</v>
@@ -4129,7 +4129,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>One aircraft (one aircraft with the N0M nose; N0P is an alternative part): 79.4 g, 12.5 h of printing.</t>
+          <t>One aircraft (one aircraft with the N0M nose; N0P is an alternative part): 79.2 g, 12.5 h of printing.</t>
         </is>
       </c>
     </row>

--- a/c7/downloads/C7/SkyG-Speed-120-BOM.xlsx
+++ b/c7/downloads/C7/SkyG-Speed-120-BOM.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Printed parts" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Order list (BOM)'!$A$4:$J$67</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Printed parts'!$A$4:$F$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Order list (BOM)'!$A$4:$J$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Printed parts'!$A$4:$F$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J67"/>
+  <dimension ref="A1:J63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="J20" s="8" t="inlineStr">
         <is>
-          <t>C7-2 aileron torque rods: twice the torsional stiffness of 2.0 mm (aileron flutter margin at 120 m/s). The wing is only 3.3 mm thick at the hinge line: the bore walls are 0.34-0.5 mm, closed by the glass skin</t>
+          <t>C7-2 aileron torque rods: twice the torsional stiffness of 2.0 mm (aileron flutter margin at 120 m/s). The wing is only 3.3 mm thick at the hinge line: the bore walls are 0.34-0.5 mm, closed by the glass skin. C7 (2026-10-07): one 90° bend per rod (horn leg 6 mm from the centreline), printed horn AHR/AHL (4.6 mm sleeve) glued on the leg; no wheel collars.</t>
         </is>
       </c>
     </row>
@@ -1300,38 +1300,38 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Tail pushrods: wire + micro ball links</t>
+          <t>Pushrods 1.2 mm with Z-bend</t>
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>0.8 mm music wire; M2 threaded solder sleeve; micro ball link M2 with 3 mm brass ball, M1.6 screw/stud + M1.6 nut (buy nuts if the pack has none)</t>
+          <t>1.2 mm steel pushrod with a factory Z-bend, &gt;= 200 mm (cut to length: 2 aileron links about 20 mm, 2 tail pushrods about 75 mm)</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>MP Jet / Hoellein micro ball joint M2, 3 mm ball (pack of 6)</t>
+          <t>Z Tip D1.2mm x 260mm Çelik Pushrod (LXMRC)</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>Tail servo arm (6.7 mm hole, Z-bend) to the horn ball</t>
+          <t>Z-bend in the servo arm (hole drilled 1.1 mm, reamed to 1.2 mm), 90° L-bend through the printed horn (reamed the same), keeper on the end</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>Class</t>
-        </is>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>Z-bend at the servo arm, ball link at the horn (takes the 55 deg skew between the servo and panel axes); link body dimensions are typical: check on receipt</t>
+          <t>Sourced</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>https://www.promodelhobby.com/urun/z-tip-d1-2mm-x-260mm-celik-pushrod-itme-cubugu (C6 simple linkage, 2026-10-06)</t>
         </is>
       </c>
     </row>
@@ -1346,38 +1346,38 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Wheel collar for 2.5 mm shaft + horn arm</t>
+          <t>Pushrod keepers for 1.2 mm wire</t>
         </is>
       </c>
       <c r="D22" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="E22" s="7" t="n">
-        <v>2</v>
-      </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t>Wheel collar for 2.5 mm shaft with set screw (flat filed on the shaft); 1 mm brass horn plate bonded to its inboard face, M1.6 hole 8 mm from the shaft</t>
+          <t>Snap-on L-type pushrod keeper for 1.2 mm wire (pack of 5)</t>
         </is>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>2.5 mm wheel collar</t>
+          <t>Pushrod Tutucu d1,2×L11mm (5 adet)</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>Stabilator shafts inside the tail module (horn along the panel normal, link ball on its inboard side)</t>
+          <t>On the protruding L-bend end at each printed horn (2 ailerons, 2 stabilators)</t>
         </is>
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>Class</t>
+          <t>Sourced</t>
         </is>
       </c>
       <c r="J22" s="8" t="inlineStr">
         <is>
-          <t>File a flat on the shaft under the set screw</t>
+          <t>Promodelhobby, Bağlantı Elemanları (in stock 2026-10-06); unclip the tail pair to remove the tail module</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Z-bend pliers</t>
+          <t>Z-bend pliers, 1.1 mm drill, 1.2 mm drill (as a hand reamer), small flat file</t>
         </is>
       </c>
       <c r="D23" s="4" t="n">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Forms Z-bends in 0.8 mm music wire</t>
+          <t>Pliers for the 90° L-bends; servo-arm and horn holes drilled 1.1 mm then reamed by hand with the 1.2 mm bit (zero play); flat file for the 0.3 mm flats</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>Tool: Z-bends at the servo arms (aileron links, tail pushrods)</t>
+          <t>Tools: servo-arm and horn holes reamed to 1.2 mm, flats on the stabilator shafts (under the printed horns) and the torque rods</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
@@ -1845,7 +1845,7 @@
       <c r="E33" s="4" t="inlineStr"/>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>22-26 AWG signal, 16 AWG power (battery and motor leads)</t>
+          <t>14 AWG red + black (battery lead and ESC feed), 16 AWG black (motor phases), 28 AWG in four colours (signals); heat shrink 1.5 / 3 / 4.8 mm</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr"/>
@@ -1859,7 +1859,11 @@
           <t>Class</t>
         </is>
       </c>
-      <c r="J33" s="5" t="inlineStr"/>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>Cut lengths per cable: Electrical Integration manual (C7, 2026-10-07)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -3011,37 +3015,37 @@
     </row>
     <row r="59">
       <c r="A59" s="4" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Controls</t>
+          <t>Test option</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Music wire 0.8 mm</t>
+          <t>Tail ballast</t>
         </is>
       </c>
       <c r="D59" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>0.8 mm spring steel, &gt;= 200 mm</t>
+          <t>Up to about 3 g</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>Music wire 0.8 mm</t>
+          <t>Tungsten putty</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>Aileron links and tail pushrods</t>
+          <t>Floor ballast cup in the tail module (x 400-410), tape over</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
@@ -3051,43 +3055,43 @@
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>Aileron: Z-bend in the 4.3 mm hole of the two-sided KST arm (0.85 mm holes), eye round a 2.0 mm drill on the horn pin; tail: Z-bend in the 6.7 mm hole, M2 solder sleeve at the ball link</t>
+          <t>Only for a heavy micro camera on SkyG Speed 60 (9 g camera: about 2.7 g)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Controls</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>Wheel collar 3/32 in</t>
+          <t>15T servo arms</t>
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E60" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F60" s="8" t="inlineStr">
         <is>
-          <t>Wheel collar for 3/32 in (2.38 mm) wire, with set screw</t>
+          <t>15T 3.9-4 mm spline arms: two-sided (aileron) with holes at 4.3 mm, one-sided (tail) with a hole at 6.7 mm; holes drilled 1.1 mm and reamed to 1.2 mm for the 1.2 mm Z-bends (no play)</t>
         </is>
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>Du-Bro 3/32 in wheel collar</t>
+          <t>Arms supplied with the ES9052MD (drill a 0.85 mm hole at the radius if missing) or a KST X06 arm set</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>On each torque-rod horn pin, outboard of the link eye</t>
+          <t>Aileron servo: two-sided arm; tail servos: one-sided arms</t>
         </is>
       </c>
       <c r="I60" s="7" t="inlineStr">
@@ -3097,43 +3101,43 @@
       </c>
       <c r="J60" s="8" t="inlineStr">
         <is>
-          <t>C7-2: on each aileron torque-rod horn pin, outboard of the link eye</t>
+          <t>Usually supplied with the servos</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Test option</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Tail ballast</t>
+          <t>XT30 series adapter (2 into 1)</t>
         </is>
       </c>
       <c r="D61" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>Up to about 3 g</t>
+          <t>XT30 series harness: two female inputs to one male output, 16 AWG</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Tungsten putty</t>
+          <t>XT30 series adapter cable (2S/series)</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>Floor ballast cup in the tail module (x 400-410), tape over</t>
+          <t>Behind the packs, under the GPS</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
@@ -3143,22 +3147,22 @@
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>Only for a heavy micro camera on SkyG Speed 60 (9 g camera: about 2.7 g)</t>
+          <t>Makes the two 3S packs one 6S pack; check polarity and series wiring with a meter before the first plug-in</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>Controls</t>
+          <t>Propulsion</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>15T servo arms</t>
+          <t>ESC capacitor</t>
         </is>
       </c>
       <c r="D62" s="7" t="n">
@@ -3169,17 +3173,17 @@
       </c>
       <c r="F62" s="8" t="inlineStr">
         <is>
-          <t>15T 3.9-4 mm spline arms with 0.85 mm holes at 4.3 mm (two-sided, aileron) and 6.7 mm (one-sided, tail)</t>
+          <t>470 uF / 35 V low-ESR electrolytic</t>
         </is>
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>Arms supplied with the ES9052MD (drill a 0.85 mm hole at the radius if missing) or a KST X06 arm set</t>
+          <t>470uF 35V low ESR capacitor</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>Aileron servo: two-sided arm; tail servos: one-sided arms</t>
+          <t>At the ESC power leads</t>
         </is>
       </c>
       <c r="I62" s="7" t="inlineStr">
@@ -3189,43 +3193,43 @@
       </c>
       <c r="J62" s="8" t="inlineStr">
         <is>
-          <t>Usually supplied with the servos</t>
+          <t>At the ESC power leads (6S voltage spikes)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Controls</t>
+          <t>Avionics</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Brass sheet 1 mm</t>
+          <t>microSD card</t>
         </is>
       </c>
       <c r="D63" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>1 mm brass, about 4 x 12 mm per horn</t>
+          <t>microSD 8-32 GB, FAT32</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>K&amp;S brass sheet 1 mm</t>
+          <t>Any microSD card</t>
         </is>
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>Tail horn plates (bonded to the wheel collars, M1.6 hole at 8 mm)</t>
+          <t>H743-WLITE slot</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr">
@@ -3235,196 +3239,12 @@
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>Solder or epoxy to the collar face</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="7" t="n">
-        <v>67</v>
-      </c>
-      <c r="B64" s="7" t="inlineStr">
-        <is>
-          <t>Hardware</t>
-        </is>
-      </c>
-      <c r="C64" s="8" t="inlineStr">
-        <is>
-          <t>M1.6 nuts</t>
-        </is>
-      </c>
-      <c r="D64" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E64" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F64" s="8" t="inlineStr">
-        <is>
-          <t>M1.6 hex nuts, steel</t>
-        </is>
-      </c>
-      <c r="G64" s="8" t="inlineStr">
-        <is>
-          <t>M1.6 nut</t>
-        </is>
-      </c>
-      <c r="H64" s="8" t="inlineStr">
-        <is>
-          <t>Tail horn ball studs (outboard of the horn plate)</t>
-        </is>
-      </c>
-      <c r="I64" s="7" t="inlineStr">
-        <is>
-          <t>Class</t>
-        </is>
-      </c>
-      <c r="J64" s="8" t="inlineStr">
-        <is>
-          <t>Thread-lock</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="4" t="n">
-        <v>68</v>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t>Power</t>
-        </is>
-      </c>
-      <c r="C65" s="5" t="inlineStr">
-        <is>
-          <t>XT30 series adapter (2 into 1)</t>
-        </is>
-      </c>
-      <c r="D65" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E65" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F65" s="5" t="inlineStr">
-        <is>
-          <t>XT30 series harness: two female inputs to one male output, 16 AWG</t>
-        </is>
-      </c>
-      <c r="G65" s="5" t="inlineStr">
-        <is>
-          <t>XT30 series adapter cable (2S/series)</t>
-        </is>
-      </c>
-      <c r="H65" s="5" t="inlineStr">
-        <is>
-          <t>Behind the packs, under the GPS</t>
-        </is>
-      </c>
-      <c r="I65" s="4" t="inlineStr">
-        <is>
-          <t>Class</t>
-        </is>
-      </c>
-      <c r="J65" s="5" t="inlineStr">
-        <is>
-          <t>Makes the two 3S packs one 6S pack; check polarity and series wiring with a meter before the first plug-in</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="7" t="n">
-        <v>69</v>
-      </c>
-      <c r="B66" s="7" t="inlineStr">
-        <is>
-          <t>Propulsion</t>
-        </is>
-      </c>
-      <c r="C66" s="8" t="inlineStr">
-        <is>
-          <t>ESC capacitor</t>
-        </is>
-      </c>
-      <c r="D66" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E66" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F66" s="8" t="inlineStr">
-        <is>
-          <t>470 uF / 35 V low-ESR electrolytic</t>
-        </is>
-      </c>
-      <c r="G66" s="8" t="inlineStr">
-        <is>
-          <t>470uF 35V low ESR capacitor</t>
-        </is>
-      </c>
-      <c r="H66" s="8" t="inlineStr">
-        <is>
-          <t>At the ESC power leads</t>
-        </is>
-      </c>
-      <c r="I66" s="7" t="inlineStr">
-        <is>
-          <t>Class</t>
-        </is>
-      </c>
-      <c r="J66" s="8" t="inlineStr">
-        <is>
-          <t>At the ESC power leads (6S voltage spikes)</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="4" t="n">
-        <v>70</v>
-      </c>
-      <c r="B67" s="4" t="inlineStr">
-        <is>
-          <t>Avionics</t>
-        </is>
-      </c>
-      <c r="C67" s="5" t="inlineStr">
-        <is>
-          <t>microSD card</t>
-        </is>
-      </c>
-      <c r="D67" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E67" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F67" s="5" t="inlineStr">
-        <is>
-          <t>microSD 8-32 GB, FAT32</t>
-        </is>
-      </c>
-      <c r="G67" s="5" t="inlineStr">
-        <is>
-          <t>Any microSD card</t>
-        </is>
-      </c>
-      <c r="H67" s="5" t="inlineStr">
-        <is>
-          <t>H743-WLITE slot</t>
-        </is>
-      </c>
-      <c r="I67" s="4" t="inlineStr">
-        <is>
-          <t>Class</t>
-        </is>
-      </c>
-      <c r="J67" s="5" t="inlineStr">
-        <is>
           <t>Logs, and the APM/scripts folder for skyg_governor.lua</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J67"/>
+  <autoFilter ref="A4:J63"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId2"/>
@@ -3432,8 +3252,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3445,7 +3266,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4126,29 +3947,133 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>AHR-aileron-horn-right</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>PLA</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>40 %</t>
+        </is>
+      </c>
+    </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>One aircraft (one aircraft with the N0M nose; N0P is an alternative part): 79.2 g, 12.5 h of printing.</t>
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>AHL-aileron-horn-left</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>PLA</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>40 %</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>THR-tail-horn-right</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>PLA</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>40 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>THL-tail-horn-left</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>PLA</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E32" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>40 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>One aircraft (one aircraft with the N0M nose; N0P is an alternative part): 80.0 g, 12.6 h of printing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Print every part with supports OFF, in the orientation of the user manual (all parts pass the print audit, design/DFAM-RULES.md).</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Only one camera nose is needed; the other noses (and their dome ring or VTX shelf) are options.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F28"/>
+  <autoFilter ref="A4:F32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>